--- a/tests/fixtures/DRO_5050_planilha_testes.xlsx
+++ b/tests/fixtures/DRO_5050_planilha_testes.xlsx
@@ -2,17 +2,17 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base" sheetId="1" r:id="Rd4b635373bca4406"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cabecalho" sheetId="2" r:id="R2892d117708f492c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sistemas_Origem" sheetId="3" r:id="R6d439acdb41041ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas_Internas" sheetId="4" r:id="Raaf299b7f3fe49b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos_Consolidados" sheetId="5" r:id="R7b189699668046d7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teste_Cabecalho" sheetId="6" r:id="R8e4a06d1680044dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teste_Obrigatorios" sheetId="7" r:id="R08a4d9c5d71345e1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teste_Formatos" sheetId="8" r:id="R0589601bfb4d4526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="9" r:id="Rb9d770d95d7f4829"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dominios" sheetId="10" r:id="R3d395c89c63448a3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia_me" sheetId="11" r:id="R1f1c32d8497a47bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Base" sheetId="1" r:id="R0b24eff1c99f407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cabecalho" sheetId="2" r:id="Ra1f5ee455ae046e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sistemas_Origem" sheetId="3" r:id="Re182f2c200f24a37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Contas_Internas" sheetId="4" r:id="R7f8bd3ca1ce04597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Eventos_Consolidados" sheetId="5" r:id="Ra93e87ef6c844261"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teste_Cabecalho" sheetId="6" r:id="R11b19aa0e5d84396"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teste_Obrigatorios" sheetId="7" r:id="R54b15b495dbf4a79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Teste_Formatos" sheetId="8" r:id="R135c08b9cdfb40c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dicionario" sheetId="9" r:id="R263ea5a8fae84ac9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dominios" sheetId="10" r:id="R1ee51259c3eb4f5e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leia_me" sheetId="11" r:id="Rb65381b208cf40af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -191,7 +191,7 @@
   <x:dxfs count="9">
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFEAF2F8"/>
         </x:patternFill>
       </x:fill>
@@ -201,7 +201,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -211,7 +211,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -221,7 +221,7 @@
         <x:color rgb="FF9C0006"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
@@ -231,7 +231,7 @@
         <x:color rgb="FF375623"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
@@ -241,28 +241,28 @@
         <x:color rgb="FF7F6000"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFE2F0D9"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFCE4D6"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
     <x:dxf>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFFF2CC"/>
         </x:patternFill>
       </x:fill>
@@ -546,9 +546,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -3689,7 +3689,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c623bf1170a4623"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7318ac984a6144ae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4603,7 +4603,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rafdc476f108c4b8b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R08cd2171b52e4e7e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4957,7 +4957,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d2f42026b3d492d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97ef2926b235480e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5021,7 +5021,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6ac4132932bf46bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf107ba70dc384564"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5125,7 +5125,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R226ee63adeeb4a1c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b1c9c17508f466e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5284,7 +5284,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R446494fbb42446ff"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa658d32a956460e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5584,7 +5584,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58a902b6b2574fc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa5634bac89e4e1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8080,7 +8080,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd650d6ae50904440"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3d737baaf64949df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9659,10 +9659,10 @@
         <x:v>ORLD-1234</x:v>
       </x:c>
       <x:c r="D15" s="14" t="str">
-        <x:v>ERRO</x:v>
+        <x:v>NORMALIZAR</x:v>
       </x:c>
       <x:c r="E15" s="14" t="str">
-        <x:v>O XSD permite apenas caracteres alfanumericos, sem hifen.</x:v>
+        <x:v>Remover hifens usados como separadores e gerar ORLD1234 no XML.</x:v>
       </x:c>
       <x:c r="F15" s="14" t="str">
         <x:v>DRO_5050_Teste_Formatos.xlsx</x:v>
@@ -10988,7 +10988,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346873264bbd4dec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33184de5c2e247e3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12227,7 +12227,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11ecfebb4c454006"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c73aa013eeb42fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>